--- a/VerveStacks_BIH_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E5DB2C-F48A-4AB1-8952-203C56BE5EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E1BBB-E92E-4032-A18B-482DF9DB4803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="362">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -775,7 +775,7 @@
     <t>elc_spv_BIH_001</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 1</t>
+    <t>solar electricity near Banja Luka (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -784,139 +784,139 @@
     <t>elc_spv_BIH_002</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 2</t>
+    <t>solar electricity near Mostar (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_BIH_003</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 3</t>
+    <t>solar electricity near Mostar (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_BIH_004</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 4</t>
+    <t>solar electricity near Mostar (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_BIH_005</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 5</t>
+    <t>solar electricity near Sarajevo (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_BIH_006</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 6</t>
+    <t>solar electricity near Cazin (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_BIH_007</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 7</t>
+    <t>solar electricity near Prijedor (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_BIH_008</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 8</t>
+    <t>solar electricity near Banja Luka (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_BIH_009</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 9</t>
+    <t>solar electricity near Prijedor (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_BIH_010</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 10</t>
+    <t>solar electricity near Sarajevo (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_BIH_011</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 11</t>
+    <t>solar electricity near Sarajevo (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_BIH_012</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 12</t>
+    <t>solar electricity near Bijeljina (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_BIH_013</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 13</t>
+    <t>solar electricity near Banja Luka (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_BIH_014</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 14</t>
+    <t>solar electricity near Doboj (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_BIH_001</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 1</t>
+    <t>wind onshore electricity near Mostar (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_BIH_002</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 2</t>
+    <t>wind onshore electricity near Sarajevo (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_BIH_003</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 3</t>
+    <t>wind onshore electricity near Mostar (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_BIH_004</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 4</t>
+    <t>wind onshore electricity near Mostar (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_BIH_005</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 5</t>
+    <t>wind onshore electricity near Bijeljina (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_BIH_006</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 6</t>
+    <t>wind onshore electricity near Bijeljina (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_BIH_007</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 7</t>
+    <t>wind onshore electricity near Prijedor (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_BIH_008</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 8</t>
+    <t>wind onshore electricity near Prijedor (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_BIH_009</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 9</t>
+    <t>wind onshore electricity near Mostar (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_BIH_010</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 10</t>
+    <t>wind onshore electricity near Banja Luka (cluster 10)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -949,18 +949,36 @@
     <t>grid node -- way/89827347-400 (Mostar, 5 km)</t>
   </si>
   <si>
+    <t>e_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>grid node -- BA4-220 (Bijeljina, 86 km)</t>
+  </si>
+  <si>
     <t>e_Prijedor_BIH</t>
   </si>
   <si>
     <t>grid node -- way/79818891-220 (Prijedor, 4 km)</t>
   </si>
   <si>
+    <t>e_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>grid node -- BA17-220 (Sarajevo, 31 km)</t>
+  </si>
+  <si>
     <t>e_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>grid node -- BA26-220 (Sarajevo, 57 km)</t>
   </si>
   <si>
+    <t>e_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>grid node -- way/251735977-220 (Banja Luka, 50 km)</t>
+  </si>
+  <si>
     <t>e_Trebinje_BIH</t>
   </si>
   <si>
@@ -970,19 +988,7 @@
     <t>e_Tuzla_BIH</t>
   </si>
   <si>
-    <t>grid node -- way/841600752-220 (Tuzla, 5 km)</t>
-  </si>
-  <si>
-    <t>e_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>grid node -- way/175002028-400 (Sarajevo, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>grid node -- BA11-220 (Zenica, 6 km)</t>
+    <t>grid node -- BA9-220 (Tuzla, 8 km)</t>
   </si>
   <si>
     <t>h_Bijeljina_BIH</t>
@@ -1009,18 +1015,36 @@
     <t>heat at grid node -- way/89827347-400 (Mostar, 5 km)</t>
   </si>
   <si>
+    <t>h_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>heat at grid node -- BA4-220 (Bijeljina, 86 km)</t>
+  </si>
+  <si>
     <t>h_Prijedor_BIH</t>
   </si>
   <si>
     <t>heat at grid node -- way/79818891-220 (Prijedor, 4 km)</t>
   </si>
   <si>
+    <t>h_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>heat at grid node -- BA17-220 (Sarajevo, 31 km)</t>
+  </si>
+  <si>
     <t>h_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>heat at grid node -- BA26-220 (Sarajevo, 57 km)</t>
   </si>
   <si>
+    <t>h_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/251735977-220 (Banja Luka, 50 km)</t>
+  </si>
+  <si>
     <t>h_Trebinje_BIH</t>
   </si>
   <si>
@@ -1030,19 +1054,7 @@
     <t>h_Tuzla_BIH</t>
   </si>
   <si>
-    <t>heat at grid node -- way/841600752-220 (Tuzla, 5 km)</t>
-  </si>
-  <si>
-    <t>h_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/175002028-400 (Sarajevo, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>heat at grid node -- BA11-220 (Zenica, 6 km)</t>
+    <t>heat at grid node -- BA9-220 (Tuzla, 8 km)</t>
   </si>
   <si>
     <t>co2_Prijedor_BIH</t>
@@ -1057,12 +1069,6 @@
     <t>co2 captured at grid node -- way/89827347-400 (Mostar, 5 km)</t>
   </si>
   <si>
-    <t>co2_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/175002028-400 (Sarajevo, 8 km)</t>
-  </si>
-  <si>
     <t>co2_Bijeljina_BIH</t>
   </si>
   <si>
@@ -1075,6 +1081,12 @@
     <t>co2 captured at grid node -- way/245190169-400 (Mostar, 86 km)</t>
   </si>
   <si>
+    <t>co2_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/251735977-220 (Banja Luka, 50 km)</t>
+  </si>
+  <si>
     <t>co2_Doboj_BIH</t>
   </si>
   <si>
@@ -1084,7 +1096,7 @@
     <t>co2_Tuzla_BIH</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/841600752-220 (Tuzla, 5 km)</t>
+    <t>co2 captured at grid node -- BA9-220 (Tuzla, 8 km)</t>
   </si>
   <si>
     <t>co2_Bratunac_BIH</t>
@@ -1093,16 +1105,22 @@
     <t>co2 captured at grid node -- BA19-220 (Zvornik, 57 km)</t>
   </si>
   <si>
-    <t>co2_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- BA11-220 (Zenica, 6 km)</t>
-  </si>
-  <si>
     <t>co2_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>co2 captured at grid node -- BA26-220 (Sarajevo, 57 km)</t>
+  </si>
+  <si>
+    <t>co2_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- BA4-220 (Bijeljina, 86 km)</t>
+  </si>
+  <si>
+    <t>co2_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- BA17-220 (Sarajevo, 31 km)</t>
   </si>
   <si>
     <t>co2s_ogci11364_BIH</t>
@@ -3523,8 +3541,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EADB88-A383-4F84-827D-8E1C4680B4DE}">
-  <dimension ref="B3:H15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4339D6A-A79A-4CCE-A702-BD86250B0654}">
+  <dimension ref="B3:H16"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
@@ -3560,13 +3578,13 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -3583,13 +3601,13 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
@@ -3606,13 +3624,13 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -3629,13 +3647,13 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
@@ -3652,13 +3670,13 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -3675,13 +3693,13 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -3698,13 +3716,13 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
@@ -3721,13 +3739,13 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
@@ -3744,13 +3762,13 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
@@ -3767,13 +3785,13 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
@@ -3790,13 +3808,13 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -3805,6 +3823,29 @@
         <v>295</v>
       </c>
       <c r="H15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" t="s">
+        <v>361</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>295</v>
+      </c>
+      <c r="H16" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3814,8 +3855,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FE7BF2-5FEF-43D9-A0AF-991ABF93453D}">
-  <dimension ref="B3:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AF7651-7265-4604-899F-CB82359EA7A5}">
+  <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -3854,13 +3895,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -3880,13 +3921,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -3906,13 +3947,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -3932,13 +3973,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -3958,13 +3999,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -3984,13 +4025,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -4010,13 +4051,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -4036,13 +4077,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -4062,13 +4103,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -4088,13 +4129,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -4106,6 +4147,32 @@
         <v>295</v>
       </c>
       <c r="I14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>336</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>337</v>
+      </c>
+      <c r="F15" t="s">
+        <v>233</v>
+      </c>
+      <c r="G15" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" t="s">
+        <v>295</v>
+      </c>
+      <c r="I15" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4115,8 +4182,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E97FBB5-4FE5-4F08-9A28-A758842436FF}">
-  <dimension ref="B3:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180AA892-5111-48C7-8D9D-6E844DCAC58B}">
+  <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -4407,6 +4474,32 @@
         <v>295</v>
       </c>
       <c r="I14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>314</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>295</v>
+      </c>
+      <c r="I15" t="s">
         <v>245</v>
       </c>
     </row>
